--- a/Base_de_donnees/Fichiers_metadonnees/videPers.xlsx
+++ b/Base_de_donnees/Fichiers_metadonnees/videPers.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Personnes&amp;Responsable_fichier" sheetId="1" state="visible" r:id="rId3"/>
@@ -48,10 +48,10 @@
     <t xml:space="preserve">Referent/Collecteur  (R/C)</t>
   </si>
   <si>
-    <t xml:space="preserve">date_debut (si R)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_fin (si R)</t>
+    <t xml:space="preserve">date_debut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_fin</t>
   </si>
   <si>
     <t xml:space="preserve">description_recolteur</t>
@@ -368,11 +368,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.9"/>
@@ -478,11 +477,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J85"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.38"/>
@@ -779,11 +777,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.87"/>
